--- a/artfynd/A 55917-2019 artfynd.xlsx
+++ b/artfynd/A 55917-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122853137</v>
       </c>
       <c r="B2" t="n">
-        <v>94836</v>
+        <v>94844</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55917-2019 artfynd.xlsx
+++ b/artfynd/A 55917-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122853137</v>
       </c>
       <c r="B2" t="n">
-        <v>94844</v>
+        <v>94846</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55917-2019 artfynd.xlsx
+++ b/artfynd/A 55917-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122853137</v>
       </c>
       <c r="B2" t="n">
-        <v>94846</v>
+        <v>94854</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55917-2019 artfynd.xlsx
+++ b/artfynd/A 55917-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122853137</v>
       </c>
       <c r="B2" t="n">
-        <v>94854</v>
+        <v>94857</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55917-2019 artfynd.xlsx
+++ b/artfynd/A 55917-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122853137</v>
       </c>
       <c r="B2" t="n">
-        <v>94857</v>
+        <v>94859</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55917-2019 artfynd.xlsx
+++ b/artfynd/A 55917-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122853137</v>
       </c>
       <c r="B2" t="n">
-        <v>94859</v>
+        <v>94865</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55917-2019 artfynd.xlsx
+++ b/artfynd/A 55917-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122853137</v>
       </c>
       <c r="B2" t="n">
-        <v>94865</v>
+        <v>94868</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
